--- a/Test2.xlsx
+++ b/Test2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20375"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237F6C1D-E9E0-4325-828D-FBBF6E478337}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D034AA2-6F85-42F3-9D5E-A83251DC9F1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="204">
   <si>
     <t xml:space="preserve">Q.1 ) </t>
   </si>
@@ -636,6 +636,15 @@
   </si>
   <si>
     <t>Draw the Chart as per giving below table</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Davies</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1422,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1952,13 +1961,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3188,7 +3191,7 @@
       <c r="D51" s="66">
         <v>33844</v>
       </c>
-      <c r="E51" s="203"/>
+      <c r="E51" s="201"/>
       <c r="F51" s="68"/>
       <c r="G51" s="2"/>
       <c r="H51" s="3"/>
@@ -3215,7 +3218,7 @@
       <c r="C53" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="204" t="str">
+      <c r="D53" s="202" t="str">
         <f ca="1">DATEDIF(D51, TODAY(), "Y") &amp; " Years"</f>
         <v>33 Years</v>
       </c>
@@ -3251,7 +3254,7 @@
       </c>
       <c r="D55" s="73" t="str">
         <f ca="1">DATEDIF(D51, TODAY(), "D") &amp; " Day"</f>
-        <v>12393 Day</v>
+        <v>12397 Day</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="3"/>
@@ -3544,9 +3547,12 @@
         <v>10</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E72" s="80"/>
+        <v>201</v>
+      </c>
+      <c r="E72" s="80" t="str">
+        <f>_xlfn.CONCAT(C72," ",D72)</f>
+        <v>Alan  Jones</v>
+      </c>
       <c r="G72" s="2"/>
       <c r="H72" s="3"/>
       <c r="K72" s="2"/>
@@ -3561,9 +3567,12 @@
         <v>11</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E73" s="80"/>
+        <v>202</v>
+      </c>
+      <c r="E73" s="80" t="str">
+        <f t="shared" ref="E73:E77" si="4">_xlfn.CONCAT(C73," ",D73)</f>
+        <v>Bob  Williams</v>
+      </c>
       <c r="G73" s="2"/>
       <c r="H73" s="3"/>
       <c r="K73" s="2"/>
@@ -3578,9 +3587,12 @@
         <v>12</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E74" s="80"/>
+        <v>203</v>
+      </c>
+      <c r="E74" s="80" t="str">
+        <f t="shared" si="4"/>
+        <v>Carol  Davies</v>
+      </c>
       <c r="G74" s="2"/>
       <c r="H74" s="3"/>
       <c r="K74" s="2"/>
@@ -3597,7 +3609,10 @@
       <c r="D75" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E75" s="80"/>
+      <c r="E75" s="80" t="str">
+        <f t="shared" si="4"/>
+        <v>Alan Jones</v>
+      </c>
       <c r="G75" s="2"/>
       <c r="H75" s="3"/>
       <c r="K75" s="2"/>
@@ -3614,7 +3629,10 @@
       <c r="D76" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E76" s="80"/>
+      <c r="E76" s="80" t="str">
+        <f t="shared" si="4"/>
+        <v>Bob Williams</v>
+      </c>
       <c r="G76" s="2"/>
       <c r="H76" s="3"/>
       <c r="K76" s="2"/>
@@ -3631,7 +3649,10 @@
       <c r="D77" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="E77" s="80"/>
+      <c r="E77" s="80" t="str">
+        <f t="shared" si="4"/>
+        <v>Carol Davies</v>
+      </c>
       <c r="G77" s="2"/>
       <c r="H77" s="3"/>
       <c r="K77" s="2"/>
@@ -3672,8 +3693,12 @@
       <c r="C83" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D83" s="80"/>
-      <c r="E83" s="80"/>
+      <c r="D83" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="80" t="s">
+        <v>55</v>
+      </c>
       <c r="G83" s="2"/>
       <c r="H83" s="3"/>
       <c r="K83" s="2"/>
@@ -3687,8 +3712,12 @@
       <c r="C84" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D84" s="80"/>
-      <c r="E84" s="80"/>
+      <c r="D84" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="80" t="s">
+        <v>56</v>
+      </c>
       <c r="G84" s="2"/>
       <c r="H84" s="3"/>
       <c r="K84" s="2"/>
@@ -3702,8 +3731,12 @@
       <c r="C85" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D85" s="80"/>
-      <c r="E85" s="80"/>
+      <c r="D85" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="80" t="s">
+        <v>57</v>
+      </c>
       <c r="G85" s="2"/>
       <c r="H85" s="3"/>
       <c r="K85" s="2"/>
@@ -3717,8 +3750,12 @@
       <c r="C86" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D86" s="80"/>
-      <c r="E86" s="80"/>
+      <c r="D86" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="80" t="s">
+        <v>55</v>
+      </c>
       <c r="G86" s="2"/>
       <c r="H86" s="3"/>
       <c r="K86" s="2"/>
@@ -3732,8 +3769,12 @@
       <c r="C87" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D87" s="80"/>
-      <c r="E87" s="80"/>
+      <c r="D87" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="80" t="s">
+        <v>56</v>
+      </c>
       <c r="G87" s="2"/>
       <c r="H87" s="3"/>
       <c r="K87" s="2"/>
@@ -3747,8 +3788,12 @@
       <c r="C88" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D88" s="80"/>
-      <c r="E88" s="80"/>
+      <c r="D88" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="80" t="s">
+        <v>57</v>
+      </c>
       <c r="G88" s="2"/>
       <c r="H88" s="3"/>
       <c r="K88" s="2"/>
@@ -4651,11 +4696,14 @@
     </row>
     <row r="169" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="170" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C170" s="205" t="s">
+      <c r="C170" s="203" t="s">
         <v>110</v>
       </c>
-      <c r="D170" s="206"/>
-      <c r="E170" s="133"/>
+      <c r="D170" s="204"/>
+      <c r="E170" s="133">
+        <f>SUMPRODUCT(D166:D168,E166:E168)</f>
+        <v>526</v>
+      </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
@@ -4799,7 +4847,7 @@
       <c r="F187" s="138"/>
       <c r="G187" s="139"/>
       <c r="H187" s="140">
-        <f t="shared" ref="H187:H197" si="4">SUM(E187:G187)</f>
+        <f t="shared" ref="H187:H197" si="5">SUM(E187:G187)</f>
         <v>0</v>
       </c>
     </row>
@@ -4814,7 +4862,7 @@
       <c r="F188" s="138"/>
       <c r="G188" s="139"/>
       <c r="H188" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4829,7 +4877,7 @@
       <c r="F189" s="138"/>
       <c r="G189" s="139"/>
       <c r="H189" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4844,7 +4892,7 @@
       <c r="F190" s="138"/>
       <c r="G190" s="139"/>
       <c r="H190" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4859,7 +4907,7 @@
       <c r="F191" s="138"/>
       <c r="G191" s="139"/>
       <c r="H191" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4874,7 +4922,7 @@
       <c r="F192" s="138"/>
       <c r="G192" s="139"/>
       <c r="H192" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4889,7 +4937,7 @@
       <c r="F193" s="138"/>
       <c r="G193" s="139"/>
       <c r="H193" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4904,7 +4952,7 @@
       <c r="F194" s="138"/>
       <c r="G194" s="139"/>
       <c r="H194" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4919,7 +4967,7 @@
       <c r="F195" s="138"/>
       <c r="G195" s="139"/>
       <c r="H195" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4934,7 +4982,7 @@
       <c r="F196" s="138"/>
       <c r="G196" s="139"/>
       <c r="H196" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4949,7 +4997,7 @@
       <c r="F197" s="138"/>
       <c r="G197" s="139"/>
       <c r="H197" s="140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -4959,19 +5007,19 @@
       </c>
       <c r="D198" s="144"/>
       <c r="E198" s="145">
-        <f t="shared" ref="E198:H198" si="5">SUM(E187:E197)</f>
+        <f t="shared" ref="E198:H198" si="6">SUM(E187:E197)</f>
         <v>0</v>
       </c>
       <c r="F198" s="145">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G198" s="146">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H198" s="147">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -5039,7 +5087,7 @@
         <v>600</v>
       </c>
       <c r="I207" s="149">
-        <f t="shared" ref="I207:I211" si="6">SUM(D207:H207)</f>
+        <f t="shared" ref="I207:I211" si="7">SUM(D207:H207)</f>
         <v>2050</v>
       </c>
     </row>
@@ -5063,7 +5111,7 @@
         <v>800</v>
       </c>
       <c r="I208" s="151">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4320</v>
       </c>
     </row>
@@ -5087,7 +5135,7 @@
         <v>275</v>
       </c>
       <c r="I209" s="151">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1375</v>
       </c>
     </row>
@@ -5111,7 +5159,7 @@
         <v>45</v>
       </c>
       <c r="I210" s="151">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>255</v>
       </c>
     </row>
@@ -5135,7 +5183,7 @@
         <v>310</v>
       </c>
       <c r="I211" s="156">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1305</v>
       </c>
     </row>
@@ -5148,23 +5196,23 @@
         <v>2100</v>
       </c>
       <c r="E212" s="159">
-        <f t="shared" ref="E212:I212" si="7">SUM(E207:E211)</f>
+        <f t="shared" ref="E212:I212" si="8">SUM(E207:E211)</f>
         <v>2360</v>
       </c>
       <c r="F212" s="159">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1985</v>
       </c>
       <c r="G212" s="159">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>830</v>
       </c>
       <c r="H212" s="160">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2030</v>
       </c>
       <c r="I212" s="161">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9305</v>
       </c>
     </row>
@@ -5360,7 +5408,7 @@
         <v>600</v>
       </c>
       <c r="I231" s="149">
-        <f t="shared" ref="I231:I235" si="8">SUM(D231:H231)</f>
+        <f t="shared" ref="I231:I235" si="9">SUM(D231:H231)</f>
         <v>2050</v>
       </c>
     </row>
@@ -5384,7 +5432,7 @@
         <v>800</v>
       </c>
       <c r="I232" s="151">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4320</v>
       </c>
     </row>
@@ -5408,7 +5456,7 @@
         <v>275</v>
       </c>
       <c r="I233" s="151">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1375</v>
       </c>
     </row>
@@ -5432,7 +5480,7 @@
         <v>45</v>
       </c>
       <c r="I234" s="151">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>255</v>
       </c>
     </row>
@@ -5456,7 +5504,7 @@
         <v>310</v>
       </c>
       <c r="I235" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1305</v>
       </c>
     </row>
@@ -5469,23 +5517,23 @@
         <v>2100</v>
       </c>
       <c r="E236" s="159">
-        <f t="shared" ref="E236:I236" si="9">SUM(E231:E235)</f>
+        <f t="shared" ref="E236:I236" si="10">SUM(E231:E235)</f>
         <v>2360</v>
       </c>
       <c r="F236" s="159">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1985</v>
       </c>
       <c r="G236" s="159">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>830</v>
       </c>
       <c r="H236" s="160">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2030</v>
       </c>
       <c r="I236" s="161">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9305</v>
       </c>
     </row>
@@ -5548,7 +5596,7 @@
       <c r="G241" s="134"/>
       <c r="H241" s="134"/>
       <c r="I241" s="162">
-        <f t="shared" ref="I241:I245" si="10">SUM(D241:H241)</f>
+        <f t="shared" ref="I241:I245" si="11">SUM(D241:H241)</f>
         <v>0</v>
       </c>
     </row>
@@ -5562,7 +5610,7 @@
       <c r="G242" s="134"/>
       <c r="H242" s="134"/>
       <c r="I242" s="162">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5576,7 +5624,7 @@
       <c r="G243" s="134"/>
       <c r="H243" s="134"/>
       <c r="I243" s="162">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5590,7 +5638,7 @@
       <c r="G244" s="134"/>
       <c r="H244" s="134"/>
       <c r="I244" s="166">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5603,23 +5651,23 @@
         <v>0</v>
       </c>
       <c r="E245" s="165">
-        <f t="shared" ref="E245:H245" si="11">SUM(E240:E244)</f>
+        <f t="shared" ref="E245:H245" si="12">SUM(E240:E244)</f>
         <v>0</v>
       </c>
       <c r="F245" s="165">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="G245" s="165">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H245" s="165">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I245" s="167">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G245" s="165">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H245" s="165">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I245" s="167">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -5680,7 +5728,10 @@
       <c r="C256" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="D256" s="169"/>
+      <c r="D256" s="169">
+        <f t="shared" ref="D256:D274" si="13">COUNTA(C256:C275)</f>
+        <v>19</v>
+      </c>
       <c r="F256" s="3"/>
       <c r="G256" s="2"/>
     </row>
@@ -5688,7 +5739,10 @@
       <c r="C257" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="D257" s="169"/>
+      <c r="D257" s="169">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
       <c r="F257" s="3"/>
       <c r="G257" s="2"/>
     </row>
@@ -5696,7 +5750,10 @@
       <c r="C258" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D258" s="169"/>
+      <c r="D258" s="169">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
       <c r="F258" s="3"/>
       <c r="G258" s="2"/>
     </row>
@@ -5704,7 +5761,10 @@
       <c r="C259" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D259" s="169"/>
+      <c r="D259" s="169">
+        <f t="shared" si="13"/>
+        <v>16</v>
+      </c>
       <c r="F259" s="3"/>
       <c r="G259" s="2"/>
     </row>
@@ -5712,7 +5772,10 @@
       <c r="C260" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="D260" s="169"/>
+      <c r="D260" s="169">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
       <c r="F260" s="3"/>
       <c r="G260" s="2"/>
     </row>
@@ -5720,7 +5783,10 @@
       <c r="C261" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="D261" s="169"/>
+      <c r="D261" s="169">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
       <c r="F261" s="3"/>
       <c r="G261" s="2"/>
     </row>
@@ -5728,7 +5794,10 @@
       <c r="C262" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="D262" s="169"/>
+      <c r="D262" s="169">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
       <c r="F262" s="3"/>
       <c r="G262" s="2"/>
     </row>
@@ -5736,7 +5805,10 @@
       <c r="C263" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="D263" s="169"/>
+      <c r="D263" s="169">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
       <c r="F263" s="3"/>
       <c r="G263" s="2"/>
     </row>
@@ -5744,7 +5816,10 @@
       <c r="C264" s="97" t="s">
         <v>80</v>
       </c>
-      <c r="D264" s="169"/>
+      <c r="D264" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F264" s="3"/>
       <c r="G264" s="2"/>
     </row>
@@ -5752,7 +5827,10 @@
       <c r="C265" s="97" t="s">
         <v>80</v>
       </c>
-      <c r="D265" s="169"/>
+      <c r="D265" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F265" s="3"/>
       <c r="G265" s="2"/>
     </row>
@@ -5760,7 +5838,10 @@
       <c r="C266" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="D266" s="169"/>
+      <c r="D266" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F266" s="3"/>
       <c r="G266" s="2"/>
     </row>
@@ -5768,7 +5849,10 @@
       <c r="C267" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="D267" s="169"/>
+      <c r="D267" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F267" s="3"/>
       <c r="G267" s="2"/>
     </row>
@@ -5776,7 +5860,10 @@
       <c r="C268" s="97" t="s">
         <v>82</v>
       </c>
-      <c r="D268" s="169"/>
+      <c r="D268" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F268" s="3"/>
       <c r="G268" s="2"/>
     </row>
@@ -5784,7 +5871,10 @@
       <c r="C269" s="97" t="s">
         <v>83</v>
       </c>
-      <c r="D269" s="169"/>
+      <c r="D269" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F269" s="3"/>
       <c r="G269" s="2"/>
     </row>
@@ -5792,7 +5882,10 @@
       <c r="C270" s="97" t="s">
         <v>84</v>
       </c>
-      <c r="D270" s="169"/>
+      <c r="D270" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F270" s="3"/>
       <c r="G270" s="2"/>
     </row>
@@ -5800,7 +5893,10 @@
       <c r="C271" s="97" t="s">
         <v>84</v>
       </c>
-      <c r="D271" s="169"/>
+      <c r="D271" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F271" s="3"/>
       <c r="G271" s="2"/>
     </row>
@@ -5808,7 +5904,10 @@
       <c r="C272" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="D272" s="169"/>
+      <c r="D272" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F272" s="3"/>
       <c r="G272" s="2"/>
     </row>
@@ -5816,7 +5915,10 @@
       <c r="C273" s="97" t="s">
         <v>137</v>
       </c>
-      <c r="D273" s="169"/>
+      <c r="D273" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F273" s="3"/>
       <c r="G273" s="2"/>
     </row>
@@ -5824,7 +5926,10 @@
       <c r="C274" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="D274" s="169"/>
+      <c r="D274" s="169">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
       <c r="F274" s="3"/>
       <c r="G274" s="2"/>
     </row>
@@ -5918,7 +6023,10 @@
       <c r="D285" s="137">
         <v>80</v>
       </c>
-      <c r="E285" s="169"/>
+      <c r="E285" s="169" t="str">
+        <f>_xlfn.IFS(D285&lt;34,"D",D285&lt;50,"C",D285&lt;70,"B",D285&lt;90,"A",D285&lt;100,"A+")</f>
+        <v>A</v>
+      </c>
       <c r="G285" s="2"/>
       <c r="J285" s="13"/>
       <c r="L285" s="14"/>
@@ -5932,7 +6040,10 @@
       <c r="D286" s="116">
         <v>50</v>
       </c>
-      <c r="E286" s="169"/>
+      <c r="E286" s="169" t="str">
+        <f t="shared" ref="E286:E304" si="14">_xlfn.IFS(D286&lt;34,"D",D286&lt;50,"C",D286&lt;70,"B",D286&lt;90,"A",D286&lt;100,"A+")</f>
+        <v>B</v>
+      </c>
       <c r="G286" s="2"/>
       <c r="J286" s="13"/>
       <c r="L286" s="14"/>
@@ -5946,7 +6057,10 @@
       <c r="D287" s="116">
         <v>60</v>
       </c>
-      <c r="E287" s="169"/>
+      <c r="E287" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>B</v>
+      </c>
       <c r="G287" s="2"/>
       <c r="J287" s="13"/>
       <c r="L287" s="14"/>
@@ -5960,7 +6074,10 @@
       <c r="D288" s="116">
         <v>95</v>
       </c>
-      <c r="E288" s="169"/>
+      <c r="E288" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A+</v>
+      </c>
       <c r="G288" s="2"/>
       <c r="J288" s="13"/>
       <c r="L288" s="14"/>
@@ -5974,7 +6091,10 @@
       <c r="D289" s="116">
         <v>20</v>
       </c>
-      <c r="E289" s="169"/>
+      <c r="E289" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>D</v>
+      </c>
       <c r="G289" s="2"/>
       <c r="J289" s="13"/>
       <c r="L289" s="14"/>
@@ -5988,7 +6108,10 @@
       <c r="D290" s="116">
         <v>40</v>
       </c>
-      <c r="E290" s="169"/>
+      <c r="E290" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>C</v>
+      </c>
       <c r="G290" s="2"/>
       <c r="J290" s="13"/>
       <c r="L290" s="14"/>
@@ -6002,7 +6125,10 @@
       <c r="D291" s="116">
         <v>10</v>
       </c>
-      <c r="E291" s="169"/>
+      <c r="E291" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>D</v>
+      </c>
       <c r="G291" s="2"/>
       <c r="J291" s="13"/>
       <c r="L291" s="14"/>
@@ -6016,7 +6142,10 @@
       <c r="D292" s="116">
         <v>80</v>
       </c>
-      <c r="E292" s="169"/>
+      <c r="E292" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A</v>
+      </c>
       <c r="G292" s="2"/>
       <c r="J292" s="13"/>
       <c r="L292" s="14"/>
@@ -6030,7 +6159,10 @@
       <c r="D293" s="116">
         <v>30</v>
       </c>
-      <c r="E293" s="169"/>
+      <c r="E293" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>D</v>
+      </c>
       <c r="G293" s="2"/>
       <c r="J293" s="13"/>
       <c r="L293" s="14"/>
@@ -6044,7 +6176,10 @@
       <c r="D294" s="116">
         <v>10</v>
       </c>
-      <c r="E294" s="169"/>
+      <c r="E294" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>D</v>
+      </c>
       <c r="G294" s="2"/>
       <c r="J294" s="13"/>
       <c r="L294" s="14"/>
@@ -6058,7 +6193,10 @@
       <c r="D295" s="116">
         <v>75</v>
       </c>
-      <c r="E295" s="169"/>
+      <c r="E295" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A</v>
+      </c>
       <c r="J295" s="13"/>
       <c r="L295" s="14"/>
       <c r="M295" s="13"/>
@@ -6071,7 +6209,10 @@
       <c r="D296" s="116">
         <v>35</v>
       </c>
-      <c r="E296" s="169"/>
+      <c r="E296" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>C</v>
+      </c>
       <c r="J296" s="13"/>
       <c r="L296" s="14"/>
       <c r="M296" s="13"/>
@@ -6084,7 +6225,10 @@
       <c r="D297" s="116">
         <v>70</v>
       </c>
-      <c r="E297" s="169"/>
+      <c r="E297" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A</v>
+      </c>
       <c r="J297" s="13"/>
       <c r="L297" s="14"/>
       <c r="M297" s="13"/>
@@ -6097,7 +6241,10 @@
       <c r="D298" s="116">
         <v>85</v>
       </c>
-      <c r="E298" s="169"/>
+      <c r="E298" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A</v>
+      </c>
       <c r="J298" s="13"/>
       <c r="L298" s="14"/>
       <c r="M298" s="13"/>
@@ -6110,7 +6257,10 @@
       <c r="D299" s="116">
         <v>30</v>
       </c>
-      <c r="E299" s="169"/>
+      <c r="E299" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>D</v>
+      </c>
       <c r="J299" s="13"/>
       <c r="L299" s="14"/>
       <c r="M299" s="13"/>
@@ -6123,7 +6273,10 @@
       <c r="D300" s="116">
         <v>60</v>
       </c>
-      <c r="E300" s="169"/>
+      <c r="E300" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>B</v>
+      </c>
       <c r="J300" s="13"/>
       <c r="L300" s="14"/>
       <c r="M300" s="13"/>
@@ -6136,7 +6289,10 @@
       <c r="D301" s="116">
         <v>90</v>
       </c>
-      <c r="E301" s="169"/>
+      <c r="E301" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A+</v>
+      </c>
       <c r="J301" s="13"/>
       <c r="L301" s="14"/>
       <c r="M301" s="13"/>
@@ -6149,7 +6305,10 @@
       <c r="D302" s="116">
         <v>70</v>
       </c>
-      <c r="E302" s="169"/>
+      <c r="E302" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A</v>
+      </c>
       <c r="J302" s="13"/>
       <c r="L302" s="14"/>
       <c r="M302" s="13"/>
@@ -6162,7 +6321,10 @@
       <c r="D303" s="116">
         <v>97</v>
       </c>
-      <c r="E303" s="169"/>
+      <c r="E303" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>A+</v>
+      </c>
       <c r="J303" s="13"/>
       <c r="L303" s="14"/>
       <c r="M303" s="13"/>
@@ -6175,7 +6337,10 @@
       <c r="D304" s="119">
         <v>20</v>
       </c>
-      <c r="E304" s="169"/>
+      <c r="E304" s="169" t="str">
+        <f t="shared" si="14"/>
+        <v>D</v>
+      </c>
       <c r="J304" s="13"/>
       <c r="L304" s="14"/>
       <c r="M304" s="13"/>
@@ -6360,7 +6525,10 @@
       <c r="D329" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="E329" s="169"/>
+      <c r="E329" s="169">
+        <f>FIND(D329,C329,1)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C330" s="9" t="s">
@@ -6369,7 +6537,10 @@
       <c r="D330" s="116" t="s">
         <v>160</v>
       </c>
-      <c r="E330" s="169"/>
+      <c r="E330" s="169">
+        <f t="shared" ref="E330:E334" si="15">FIND(D330,C330,1)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C331" s="9" t="s">
@@ -6378,7 +6549,10 @@
       <c r="D331" s="116" t="s">
         <v>162</v>
       </c>
-      <c r="E331" s="169"/>
+      <c r="E331" s="169">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C332" s="9" t="s">
@@ -6387,7 +6561,10 @@
       <c r="D332" s="116" t="s">
         <v>164</v>
       </c>
-      <c r="E332" s="169"/>
+      <c r="E332" s="169">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C333" s="9" t="s">
@@ -6396,7 +6573,10 @@
       <c r="D333" s="116" t="s">
         <v>165</v>
       </c>
-      <c r="E333" s="169"/>
+      <c r="E333" s="169">
+        <f t="shared" si="15"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="334" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C334" s="11" t="s">
@@ -6405,7 +6585,10 @@
       <c r="D334" s="119" t="s">
         <v>166</v>
       </c>
-      <c r="E334" s="169"/>
+      <c r="E334" s="169">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
@@ -6527,7 +6710,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C356" s="7">
         <v>20</v>
       </c>
@@ -6540,10 +6723,16 @@
       <c r="F356" s="176">
         <v>10</v>
       </c>
-      <c r="G356" s="177"/>
-      <c r="H356" s="178"/>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G356" s="177">
+        <f>MIN(C356:F356)</f>
+        <v>10</v>
+      </c>
+      <c r="H356" s="178">
+        <f>MAX(C356:F356)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C357" s="9">
         <v>40</v>
       </c>
@@ -6556,10 +6745,16 @@
       <c r="F357" s="179">
         <v>10</v>
       </c>
-      <c r="G357" s="180"/>
-      <c r="H357" s="108"/>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G357" s="177">
+        <f>MIN(C357:F357)</f>
+        <v>10</v>
+      </c>
+      <c r="H357" s="178">
+        <f t="shared" ref="H357:H360" si="16">MAX(C357:F357)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C358" s="9">
         <v>10</v>
       </c>
@@ -6572,10 +6767,16 @@
       <c r="F358" s="179">
         <v>20</v>
       </c>
-      <c r="G358" s="180"/>
-      <c r="H358" s="108"/>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G358" s="177">
+        <f t="shared" ref="G358:G360" si="17">MIN(C358:F358)</f>
+        <v>10</v>
+      </c>
+      <c r="H358" s="178">
+        <f t="shared" si="16"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C359" s="9">
         <v>20</v>
       </c>
@@ -6588,8 +6789,14 @@
       <c r="F359" s="179">
         <v>10</v>
       </c>
-      <c r="G359" s="180"/>
-      <c r="H359" s="108"/>
+      <c r="G359" s="177">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="H359" s="178">
+        <f t="shared" si="16"/>
+        <v>99</v>
+      </c>
     </row>
     <row r="360" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C360" s="11">
@@ -6601,11 +6808,17 @@
       <c r="E360" s="79">
         <v>20</v>
       </c>
-      <c r="F360" s="181">
+      <c r="F360" s="180">
         <v>99</v>
       </c>
-      <c r="G360" s="182"/>
-      <c r="H360" s="110"/>
+      <c r="G360" s="177">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="H360" s="178">
+        <f t="shared" si="16"/>
+        <v>99</v>
+      </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
@@ -6633,40 +6846,40 @@
       <c r="C368" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D368" s="183">
+      <c r="D368" s="181">
         <v>11500</v>
       </c>
-      <c r="E368" s="184">
+      <c r="E368" s="182">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F368" s="185"/>
-      <c r="G368" s="186"/>
+      <c r="F368" s="183"/>
+      <c r="G368" s="184"/>
     </row>
     <row r="369" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C369" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D369" s="187">
+      <c r="D369" s="185">
         <v>12500</v>
       </c>
-      <c r="E369" s="188">
+      <c r="E369" s="186">
         <v>0.10299999999999999</v>
       </c>
-      <c r="F369" s="189"/>
-      <c r="G369" s="186"/>
+      <c r="F369" s="187"/>
+      <c r="G369" s="184"/>
     </row>
     <row r="370" spans="3:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C370" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D370" s="190">
+      <c r="D370" s="188">
         <v>13200</v>
       </c>
-      <c r="E370" s="191">
+      <c r="E370" s="189">
         <v>0.1236</v>
       </c>
-      <c r="F370" s="192"/>
-      <c r="G370" s="186"/>
+      <c r="F370" s="190"/>
+      <c r="G370" s="184"/>
     </row>
     <row r="373" spans="3:8" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C373" s="5" t="s">
@@ -6678,7 +6891,7 @@
       <c r="E373" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F373" s="193" t="s">
+      <c r="F373" s="191" t="s">
         <v>189</v>
       </c>
     </row>
@@ -6686,80 +6899,80 @@
       <c r="C374" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D374" s="183">
+      <c r="D374" s="181">
         <v>250</v>
       </c>
-      <c r="E374" s="184">
+      <c r="E374" s="182">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F374" s="194"/>
-      <c r="G374" s="186"/>
-      <c r="H374" s="195"/>
+      <c r="F374" s="192"/>
+      <c r="G374" s="184"/>
+      <c r="H374" s="193"/>
     </row>
     <row r="375" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C375" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D375" s="187">
+      <c r="D375" s="185">
         <v>280</v>
       </c>
-      <c r="E375" s="188">
+      <c r="E375" s="186">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F375" s="196"/>
-      <c r="G375" s="186"/>
+      <c r="F375" s="194"/>
+      <c r="G375" s="184"/>
     </row>
     <row r="376" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C376" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="D376" s="187">
+      <c r="D376" s="185">
         <v>320</v>
       </c>
-      <c r="E376" s="188">
+      <c r="E376" s="186">
         <v>0.10299999999999999</v>
       </c>
-      <c r="F376" s="196"/>
-      <c r="G376" s="186"/>
+      <c r="F376" s="194"/>
+      <c r="G376" s="184"/>
     </row>
     <row r="377" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C377" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D377" s="187">
+      <c r="D377" s="185">
         <v>750</v>
       </c>
-      <c r="E377" s="188">
+      <c r="E377" s="186">
         <v>0.1236</v>
       </c>
-      <c r="F377" s="196"/>
-      <c r="G377" s="186"/>
+      <c r="F377" s="194"/>
+      <c r="G377" s="184"/>
     </row>
     <row r="378" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C378" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="D378" s="187">
+      <c r="D378" s="185">
         <v>550</v>
       </c>
-      <c r="E378" s="188">
+      <c r="E378" s="186">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F378" s="196"/>
-      <c r="G378" s="186"/>
+      <c r="F378" s="194"/>
+      <c r="G378" s="184"/>
     </row>
     <row r="379" spans="3:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C379" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D379" s="190">
+      <c r="D379" s="188">
         <v>800</v>
       </c>
-      <c r="E379" s="191">
+      <c r="E379" s="189">
         <v>0.10299999999999999</v>
       </c>
-      <c r="F379" s="197"/>
-      <c r="G379" s="186"/>
+      <c r="F379" s="195"/>
+      <c r="G379" s="184"/>
     </row>
     <row r="382" spans="3:8" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C382" s="5" t="s">
@@ -6771,7 +6984,7 @@
       <c r="E382" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F382" s="193" t="s">
+      <c r="F382" s="191" t="s">
         <v>193</v>
       </c>
     </row>
@@ -6779,78 +6992,78 @@
       <c r="C383" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D383" s="183">
+      <c r="D383" s="181">
         <v>225</v>
       </c>
-      <c r="E383" s="184">
+      <c r="E383" s="182">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F383" s="194"/>
-      <c r="G383" s="198"/>
-      <c r="H383" s="195"/>
+      <c r="F383" s="192"/>
+      <c r="G383" s="196"/>
+      <c r="H383" s="193"/>
     </row>
     <row r="384" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C384" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="D384" s="187">
+      <c r="D384" s="185">
         <v>180</v>
       </c>
-      <c r="E384" s="188">
+      <c r="E384" s="186">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F384" s="196"/>
-      <c r="G384" s="199"/>
+      <c r="F384" s="194"/>
+      <c r="G384" s="197"/>
       <c r="H384" s="51"/>
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C385" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="D385" s="187">
+      <c r="D385" s="185">
         <v>430</v>
       </c>
-      <c r="E385" s="188">
+      <c r="E385" s="186">
         <v>0.10299999999999999</v>
       </c>
-      <c r="F385" s="196"/>
-      <c r="H385" s="200"/>
+      <c r="F385" s="194"/>
+      <c r="H385" s="198"/>
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C386" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D386" s="187">
+      <c r="D386" s="185">
         <v>340</v>
       </c>
-      <c r="E386" s="188">
+      <c r="E386" s="186">
         <v>0.1236</v>
       </c>
-      <c r="F386" s="196"/>
+      <c r="F386" s="194"/>
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C387" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="D387" s="187">
+      <c r="D387" s="185">
         <v>730</v>
       </c>
-      <c r="E387" s="188">
+      <c r="E387" s="186">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F387" s="196"/>
+      <c r="F387" s="194"/>
     </row>
     <row r="388" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C388" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D388" s="190">
+      <c r="D388" s="188">
         <v>670</v>
       </c>
-      <c r="E388" s="191">
+      <c r="E388" s="189">
         <v>0.10299999999999999</v>
       </c>
-      <c r="F388" s="197"/>
+      <c r="F388" s="195"/>
     </row>
     <row r="391" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
@@ -6918,7 +7131,7 @@
       <c r="P395"/>
     </row>
     <row r="398" spans="1:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="A398" s="201"/>
+      <c r="A398" s="199"/>
       <c r="D398"/>
     </row>
     <row r="399" spans="1:16" ht="15" x14ac:dyDescent="0.25">
@@ -6931,7 +7144,7 @@
       <c r="D399"/>
     </row>
     <row r="400" spans="1:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="A400" s="202"/>
+      <c r="A400" s="200"/>
       <c r="B400"/>
       <c r="C400"/>
       <c r="D400"/>
@@ -7008,7 +7221,7 @@
         <v>600</v>
       </c>
       <c r="I403" s="149">
-        <f t="shared" ref="I403:I407" si="12">SUM(D403:H403)</f>
+        <f t="shared" ref="I403:I407" si="18">SUM(D403:H403)</f>
         <v>2050</v>
       </c>
       <c r="J403"/>
@@ -7037,7 +7250,7 @@
         <v>800</v>
       </c>
       <c r="I404" s="151">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>4320</v>
       </c>
       <c r="J404"/>
@@ -7066,7 +7279,7 @@
         <v>275</v>
       </c>
       <c r="I405" s="151">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1375</v>
       </c>
       <c r="J405"/>
@@ -7095,7 +7308,7 @@
         <v>45</v>
       </c>
       <c r="I406" s="151">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>255</v>
       </c>
       <c r="J406"/>
@@ -7124,7 +7337,7 @@
         <v>310</v>
       </c>
       <c r="I407" s="156">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1305</v>
       </c>
       <c r="J407"/>
@@ -7142,23 +7355,23 @@
         <v>2100</v>
       </c>
       <c r="E408" s="159">
-        <f t="shared" ref="E408:I408" si="13">SUM(E403:E407)</f>
+        <f t="shared" ref="E408:I408" si="19">SUM(E403:E407)</f>
         <v>2360</v>
       </c>
       <c r="F408" s="159">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>1985</v>
       </c>
       <c r="G408" s="159">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>830</v>
       </c>
       <c r="H408" s="160">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>2030</v>
       </c>
       <c r="I408" s="161">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>9305</v>
       </c>
       <c r="J408"/>
@@ -7265,7 +7478,7 @@
       <c r="M415"/>
     </row>
     <row r="418" spans="1:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="A418" s="202"/>
+      <c r="A418" s="200"/>
       <c r="B418"/>
       <c r="C418"/>
       <c r="D418"/>
@@ -7302,7 +7515,7 @@
       <c r="I420"/>
       <c r="J420"/>
       <c r="K420"/>
-      <c r="L420" s="202"/>
+      <c r="L420" s="200"/>
       <c r="M420"/>
       <c r="N420"/>
       <c r="O420"/>

--- a/Test2.xlsx
+++ b/Test2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D034AA2-6F85-42F3-9D5E-A83251DC9F1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A7FAEF-0A83-4FF6-8A2B-5CCAED2EEC33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D55" s="73" t="str">
         <f ca="1">DATEDIF(D51, TODAY(), "D") &amp; " Day"</f>
-        <v>12397 Day</v>
+        <v>12401 Day</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="3"/>
